--- a/stories/arbres/ATOM-SEC.RUE.001-08.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dominique marche avec papa. Ils vont au parc. Dominique sent les tilleuls. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Dominique s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Dominique sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Papa dit : on s'arrête. Pieds au bord. Sur le trottoir. Dominique pose les pieds au bord. Les pieds sont calmes. Papa tient sa main. Papa dit : bravo Dominique. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
+          <t>Dominique marche avec papa. Ils vont au parc. Dominique sent les tilleuls. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Dominique s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Dominique sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. On s'arrête. Pieds au bord. Sur le trottoir. Dominique pose les pieds au bord. Les pieds sont calmes. Papa tient sa main. Bravo Dominique. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Dominique marche avec papa. Ils vont au parc. Dominique sent les tilleuls. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Dominique s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Dominique sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir.
+papa|On s'arrête. Pieds au bord. Sur le trottoir.
+narrateur|Dominique pose les pieds au bord. Les pieds sont calmes. Papa tient sa main.
+papa|Bravo Dominique. On s'arrête au trottoir. On attend avec papa.
+narrateur|Les pieds restent au bord du trottoir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Dominique arrive au bord. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Dominique s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1842,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Dominique donne la main à papa. Ils attendent un moment.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2009,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2049,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-08.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Dominique arrive au bord. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1687,7 @@
           <t>narrateur|Dominique s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1847,6 +1859,7 @@
           <t>narrateur|Dominique donne la main à papa. Ils attendent un moment.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2014,6 +2027,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2070,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2257,6 +2285,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.001-08.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dominique s'arrête au trottoir</t>
+          <t>Les tilleuls de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les tilleuls sentent le miel tiède. Raphaël et papa vont au parc. Le doudou est dans la poche. Au bord, Raphaël s'arrête. Pieds au bord, sur le trottoir.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dominique marche avec papa. Ils vont au parc. Dominique sent les tilleuls. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Dominique s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Dominique sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. On s'arrête. Pieds au bord. Sur le trottoir. Dominique pose les pieds au bord. Les pieds sont calmes. Papa tient sa main. Bravo Dominique. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
+          <t>Les tilleuls sentent le miel tiède. Une abeille passe, tout près des fleurs. Elle fait un petit bzz. L'ombre de la grille raye le chemin. Les rayures sont longues, un peu bleues. Un doudou bleu dort dans la poche. La poche est chaude, un peu rêche. Raphaël vit ici, avec papa. Papa, ça sent le miel ! Oui. Les tilleuls sont en fleurs. On va au parc ? Oui ! Tu mets tes chaussures ? En ce moment, Raphaël s'accroupit. Il enfile la chaussure gauche. Puis la chaussure droite. Tu as fini tes chaussures ? Oui, papa. Bravo. Le doudou reste dans la poche ? Oui. Papa ouvre le petit portillon. L'air sent le miel et l'herbe. Bzz, l'abeille ! Elle butine. On marche sur le trottoir. Raphaël donne la main à papa. Les rayures d'ombre glissent sur les pieds. Les tilleuls sont plus près. Le doudou fait un petit paquet chaud. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Raphaël s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Le miel sent encore plus fort. Raphaël serre la main de papa. Bravo, Raphaël. Tu as fait du bon travail. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,10 +1324,56 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Dominique marche avec papa. Ils vont au parc. Dominique sent les tilleuls. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Dominique s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Dominique sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir.
-papa|On s'arrête. Pieds au bord. Sur le trottoir.
-narrateur|Dominique pose les pieds au bord. Les pieds sont calmes. Papa tient sa main.
-papa|Bravo Dominique. On s'arrête au trottoir. On attend avec papa.
+          <t>narrateur|Les tilleuls sentent le miel tiède.
+narrateur|Une abeille passe, tout près des fleurs.
+narrateur|Elle fait un petit bzz.
+narrateur|L'ombre de la grille raye le chemin.
+narrateur|Les rayures sont longues, un peu bleues.
+narrateur|Un doudou bleu dort dans la poche.
+narrateur|La poche est chaude, un peu rêche.
+narrateur|Raphaël vit ici, avec papa.
+enfant-m|Papa, ça sent le miel !
+papa|Oui.
+papa|Les tilleuls sont en fleurs.
+papa|On va au parc ?
+enfant-m|Oui !
+papa|Tu mets tes chaussures ?
+narrateur|En ce moment, Raphaël s'accroupit.
+narrateur|Il enfile la chaussure gauche.
+narrateur|Puis la chaussure droite.
+papa|Tu as fini tes chaussures ?
+enfant-m|Oui, papa.
+papa|Bravo.
+papa|Le doudou reste dans la poche ?
+enfant-m|Oui.
+narrateur|Papa ouvre le petit portillon.
+narrateur|L'air sent le miel et l'herbe.
+enfant-m|Bzz, l'abeille !
+papa|Elle butine.
+papa|On marche sur le trottoir.
+narrateur|Raphaël donne la main à papa.
+narrateur|Les rayures d'ombre glissent sur les pieds.
+narrateur|Les tilleuls sont plus près.
+narrateur|Le doudou fait un petit paquet chaud.
+papa|On reste sur le trottoir.
+narrateur|Le bord du trottoir arrive.
+narrateur|Le bord est gris et net.
+papa|On va s'arrêter.
+papa|Pieds au bord.
+papa|Sur le trottoir.
+narrateur|Raphaël s'arrête.
+narrateur|Ses pieds sont au bord.
+narrateur|Les pieds restent au bord.
+narrateur|Les pieds sont sur le trottoir.
+enfant-m|Je m'arrête.
+papa|Oui.
+papa|On attend avec papa.
+papa|Tes pieds sont calmes ?
+enfant-m|Oui.
+narrateur|Le miel sent encore plus fort.
+narrateur|Raphaël serre la main de papa.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
@@ -1348,7 +1406,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Dominique arrive au bord. Que fait-il ?</t>
+          <t>Raphaël arrive au bord. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,7 +1566,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Dominique arrive au bord. Que fait-il ?</t>
+          <t>narrateur|Raphaël arrive au bord.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1595,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dominique s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+          <t>Raphaël s'arrête au bord. Les pieds sont sur le trottoir. Les pieds restent au bord. Tu t'arrêtes au trottoir ? Oui. Je m'arrête. Bravo, Raphaël. On attend avec papa. La main de papa est chaude. Le doudou reste dans la poche. L'abeille fait encore bzz, loin.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1684,7 +1743,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Dominique s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+          <t>narrateur|Raphaël s'arrête au bord.
+narrateur|Les pieds sont sur le trottoir.
+narrateur|Les pieds restent au bord.
+papa|Tu t'arrêtes au trottoir ?
+enfant-m|Oui.
+enfant-m|Je m'arrête.
+papa|Bravo, Raphaël.
+papa|On attend avec papa.
+narrateur|La main de papa est chaude.
+narrateur|Le doudou reste dans la poche.
+narrateur|L'abeille fait encore bzz, loin.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1712,7 +1781,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Dominique donne la main à papa. Ils attendent un moment.</t>
+          <t>On y va ensemble ? Oui, papa. Ils marchent avec l'adulte. Le parc sent le miel et l'herbe. Un banc est à l'ombre. Tu sors le doudou ? Raphaël le pose sur le banc. Il a de l'ombre. Oui. Tu as fini de le poser ? Oui. Bravo. Les tilleuls bougent un peu. L'ombre de la grille reste derrière eux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1856,10 +1925,27 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Dominique donne la main à papa. Ils attendent un moment.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>papa|On y va ensemble ?
+enfant-m|Oui, papa.
+narrateur|Ils marchent avec l'adulte.
+narrateur|Le parc sent le miel et l'herbe.
+narrateur|Un banc est à l'ombre.
+papa|Tu sors le doudou ?
+narrateur|Raphaël le pose sur le banc.
+enfant-m|Il a de l'ombre.
+papa|Oui.
+papa|Tu as fini de le poser ?
+enfant-m|Oui.
+papa|Bravo.
+narrateur|Les tilleuls bougent un peu.
+narrateur|L'ombre de la grille reste derrière eux.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1884,7 +1970,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je me suis arrêté. Pieds au bord. Sur le trottoir. Bravo, Raphaël. Le doudou bleu dort à l'ombre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2024,7 +2110,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Je me suis arrêté.
+papa|Pieds au bord.
+papa|Sur le trottoir.
+papa|Bravo, Raphaël.
+narrateur|Le doudou bleu dort à l'ombre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2046,7 +2137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2084,6 +2175,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-08.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-08.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les tilleuls sentent le miel tiède. Une abeille passe, tout près des fleurs. Elle fait un petit bzz. L'ombre de la grille raye le chemin. Les rayures sont longues, un peu bleues. Un doudou bleu dort dans la poche. La poche est chaude, un peu rêche. Raphaël vit ici, avec papa. Papa, ça sent le miel ! Oui. Les tilleuls sont en fleurs. On va au parc ? Oui ! Tu mets tes chaussures ? En ce moment, Raphaël s'accroupit. Il enfile la chaussure gauche. Puis la chaussure droite. Tu as fini tes chaussures ? Oui, papa. Bravo. Le doudou reste dans la poche ? Oui. Papa ouvre le petit portillon. L'air sent le miel et l'herbe. Bzz, l'abeille ! Elle butine. On marche sur le trottoir. Raphaël donne la main à papa. Les rayures d'ombre glissent sur les pieds. Les tilleuls sont plus près. Le doudou fait un petit paquet chaud. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Raphaël s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Le miel sent encore plus fort. Raphaël serre la main de papa. Bravo, Raphaël. Tu as fait du bon travail. Les pieds restent au bord du trottoir.</t>
+          <t>Les tilleuls sentent le miel tiède. Une abeille passe, tout près des fleurs. Elle fait un petit bzz. L'ombre de la grille raye le chemin. Les rayures sont longues, un peu bleues. Un doudou bleu dort dans la poche. La poche est chaude, un peu rêche. Raphaël vit ici, avec papa. Papa, ça sent le miel ! Oui. Les tilleuls sont en fleurs. On va au parc ? Oui ! Tu mets tes chaussures ? En ce moment, Raphaël s'accroupit. Il enfile la chaussure gauche. Puis la chaussure droite. Tu as fini tes chaussures ? Oui, papa. Bravo. Le doudou reste dans la poche ? Oui. Papa ouvre le petit portillon. L'air sent le miel et l'herbe. Bzz, l'abeille ! Elle butine. On marche sur le trottoir. Raphaël donne la main à papa. Les rayures d'ombre glissent sur les pieds. Les tilleuls sont plus près. Le doudou fait un petit paquet chaud. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Raphaël s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Le miel sent encore plus fort. Raphaël serre la main de papa. Bravo, Raphaël. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Dominique marche avec papa. Ils vont au parc. Dominique sent les tilleuls. Ils arrivent au bord. Le bord du &lt;emphasis level="moderate"&gt;trottoir&lt;/emphasis&gt; est là. Papa s'arrête. Dominique s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Dominique sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Papa dit : on s'arrête. Pieds au bord. Sur le trottoir. Dominique pose les pieds au bord. Les pieds sont calmes. Papa tient sa main. Papa dit : bravo Dominique. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les tilleuls sentent le miel tiède. Une abeille passe, tout près des fleurs. Elle fait un petit bzz. L'ombre de la grille raye le chemin. Les rayures sont longues, un peu bleues. Un doudou bleu dort dans la poche. La poche est chaude, un peu rêche. Raphaël vit ici, avec papa. Papa, ça sent le miel ! Oui. Les tilleuls sont en fleurs. On va au parc ? Oui ! Tu mets tes chaussures ? En ce moment, Raphaël s'accroupit. Il enfile la chaussure gauche. Puis la chaussure droite. Tu as fini tes chaussures ? Oui, papa. Bravo. Le doudou reste dans la poche ? Oui. Papa ouvre le petit portillon. L'air sent le miel et l'herbe. Bzz, l'abeille ! Elle butine. On marche sur le trottoir. Raphaël donne la main à papa. Les rayures d'ombre glissent sur les pieds. Les tilleuls sont plus près. Le doudou fait un petit paquet chaud. On reste sur le trottoir. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Raphaël s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Le miel sent encore plus fort. Raphaël serre la main de papa. Bravo, Raphaël. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1373,7 +1373,6 @@
 narrateur|Le miel sent encore plus fort.
 narrateur|Raphaël serre la main de papa.
 papa|Bravo, Raphaël.
-papa|Tu as fait du bon travail.
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
@@ -1411,7 +1410,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Dominique arrive au bord. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël arrive au bord. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1570,7 +1569,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1600,7 +1598,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Dominique s'arrête au bord. Les pieds sont sur le &lt;emphasis level="moderate"&gt;trottoir&lt;/emphasis&gt;. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël s'arrête au bord. Les pieds sont sur le trottoir. Les pieds restent au bord. Tu t'arrêtes au trottoir ? Oui. Je m'arrête. Bravo, Raphaël. On attend avec papa. La main de papa est chaude. Le doudou reste dans la poche. L'abeille fait encore bzz, loin.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1756,7 +1754,6 @@
 narrateur|L'abeille fait encore bzz, loin.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1786,7 +1783,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Dominique donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; à papa. Ils attendent un moment.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On y va ensemble ? Oui, papa. Ils marchent avec l'adulte. Le parc sent le miel et l'herbe. Un banc est à l'ombre. Tu sors le doudou ? Raphaël le pose sur le banc. Il a de l'ombre. Oui. Tu as fini de le poser ? Oui. Bravo. Les tilleuls bougent un peu. L'ombre de la grille reste derrière eux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1970,12 +1967,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je me suis arrêté. Pieds au bord. Sur le trottoir. Bravo, Raphaël. Le doudou bleu dort à l'ombre. L'histoire est finie.</t>
+          <t>Je me suis arrêté. Pieds au bord. Sur le trottoir. Bravo, Raphaël. Le doudou bleu dort à l'ombre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je me suis arrêté. Pieds au bord. Sur le trottoir. Bravo, Raphaël. Le doudou bleu dort à l'ombre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2114,11 +2111,9 @@
 papa|Pieds au bord.
 papa|Sur le trottoir.
 papa|Bravo, Raphaël.
-narrateur|Le doudou bleu dort à l'ombre.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le doudou bleu dort à l'ombre.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2137,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2182,6 +2177,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-08.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-08.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trajet vers le parc</t>
+          <t>jardin de devant, trottoir vers le parc aux tilleuls</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dominique, papa</t>
+          <t>Raphaël, papa</t>
         </is>
       </c>
     </row>
